--- a/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
@@ -675,11 +675,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.282054" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.424911" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="7.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
@@ -677,7 +677,7 @@
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="7.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
   </x:cols>
